--- a/314e-ig/output/CodeSystem-time-precision-units-cs.xlsx
+++ b/314e-ig/output/CodeSystem-time-precision-units-cs.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="56">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-16T16:45:26+05:30</t>
+    <t>2026-05-17T00:25:02+05:30</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -174,13 +174,10 @@
     <t>months</t>
   </si>
   <si>
-    <t>y</t>
+    <t>a</t>
   </si>
   <si>
     <t>years</t>
-  </si>
-  <si>
-    <t>n</t>
   </si>
   <si>
     <t>none</t>
@@ -600,7 +597,7 @@
         <v>55</v>
       </c>
       <c r="C9" t="s" s="2">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D9" s="2"/>
     </row>

--- a/314e-ig/output/CodeSystem-time-precision-units-cs.xlsx
+++ b/314e-ig/output/CodeSystem-time-precision-units-cs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-17T00:25:02+05:30</t>
+    <t>2026-05-19T06:46:39+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/CodeSystem-time-precision-units-cs.xlsx
+++ b/314e-ig/output/CodeSystem-time-precision-units-cs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-19T06:46:39+05:30</t>
+    <t>2026-05-19T11:54:54+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/CodeSystem-time-precision-units-cs.xlsx
+++ b/314e-ig/output/CodeSystem-time-precision-units-cs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-19T11:54:54+05:30</t>
+    <t>2026-05-25T12:07:44+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/CodeSystem-time-precision-units-cs.xlsx
+++ b/314e-ig/output/CodeSystem-time-precision-units-cs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-25T12:07:44+05:30</t>
+    <t>2026-05-25T12:34:12+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/CodeSystem-time-precision-units-cs.xlsx
+++ b/314e-ig/output/CodeSystem-time-precision-units-cs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-25T12:34:12+05:30</t>
+    <t>2026-05-25T13:52:53+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/CodeSystem-time-precision-units-cs.xlsx
+++ b/314e-ig/output/CodeSystem-time-precision-units-cs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-25T13:52:53+05:30</t>
+    <t>2026-05-25T14:14:21+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/CodeSystem-time-precision-units-cs.xlsx
+++ b/314e-ig/output/CodeSystem-time-precision-units-cs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-25T14:14:21+05:30</t>
+    <t>2026-05-25T14:26:28+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/CodeSystem-time-precision-units-cs.xlsx
+++ b/314e-ig/output/CodeSystem-time-precision-units-cs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-25T14:26:28+05:30</t>
+    <t>2026-05-25T14:41:34+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/CodeSystem-time-precision-units-cs.xlsx
+++ b/314e-ig/output/CodeSystem-time-precision-units-cs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-25T14:41:34+05:30</t>
+    <t>2026-05-25T15:12:42+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/CodeSystem-time-precision-units-cs.xlsx
+++ b/314e-ig/output/CodeSystem-time-precision-units-cs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-25T15:12:42+05:30</t>
+    <t>2026-05-25T15:24:41+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/CodeSystem-time-precision-units-cs.xlsx
+++ b/314e-ig/output/CodeSystem-time-precision-units-cs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-25T15:24:41+05:30</t>
+    <t>2026-05-25T15:48:57+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/CodeSystem-time-precision-units-cs.xlsx
+++ b/314e-ig/output/CodeSystem-time-precision-units-cs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-25T15:48:57+05:30</t>
+    <t>2026-05-25T16:36:06+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/CodeSystem-time-precision-units-cs.xlsx
+++ b/314e-ig/output/CodeSystem-time-precision-units-cs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-25T16:36:06+05:30</t>
+    <t>2026-05-26T08:48:22+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/CodeSystem-time-precision-units-cs.xlsx
+++ b/314e-ig/output/CodeSystem-time-precision-units-cs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-26T08:48:22+05:30</t>
+    <t>2026-05-26T12:06:33+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/CodeSystem-time-precision-units-cs.xlsx
+++ b/314e-ig/output/CodeSystem-time-precision-units-cs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-26T12:06:33+05:30</t>
+    <t>2026-05-26T19:54:55+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/CodeSystem-time-precision-units-cs.xlsx
+++ b/314e-ig/output/CodeSystem-time-precision-units-cs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-26T19:54:55+05:30</t>
+    <t>2026-06-10T16:33:40+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/CodeSystem-time-precision-units-cs.xlsx
+++ b/314e-ig/output/CodeSystem-time-precision-units-cs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-10T16:33:40+05:30</t>
+    <t>2026-06-11T14:17:09+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/CodeSystem-time-precision-units-cs.xlsx
+++ b/314e-ig/output/CodeSystem-time-precision-units-cs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-11T14:17:09+05:30</t>
+    <t>2026-06-18T13:36:33+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/CodeSystem-time-precision-units-cs.xlsx
+++ b/314e-ig/output/CodeSystem-time-precision-units-cs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T13:36:33+05:30</t>
+    <t>2026-06-18T14:15:04+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/CodeSystem-time-precision-units-cs.xlsx
+++ b/314e-ig/output/CodeSystem-time-precision-units-cs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T14:15:04+05:30</t>
+    <t>2026-06-18T16:14:31+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/CodeSystem-time-precision-units-cs.xlsx
+++ b/314e-ig/output/CodeSystem-time-precision-units-cs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T16:14:31+05:30</t>
+    <t>2026-06-24T16:34:23+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/CodeSystem-time-precision-units-cs.xlsx
+++ b/314e-ig/output/CodeSystem-time-precision-units-cs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-24T16:34:23+05:30</t>
+    <t>2026-06-29T17:18:47+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/CodeSystem-time-precision-units-cs.xlsx
+++ b/314e-ig/output/CodeSystem-time-precision-units-cs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T17:18:47+05:30</t>
+    <t>2026-07-01T18:18:44+05:30</t>
   </si>
   <si>
     <t>Publisher</t>
